--- a/sample/폼주문 주문정보.xlsx
+++ b/sample/폼주문 주문정보.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="45">
   <si>
     <t>응답일시</t>
   </si>
@@ -101,6 +101,78 @@
   </si>
   <si>
     <t>샤넬 카드지갑 은색 5번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아무거나 샀는데 아무거나 샀어 아무거나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 강동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 논현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천 서구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경북 포항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제주시 성산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보세가방 32cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴대폰 액세서리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피부에 안좋은 화장품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기억안남</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입금할까말까</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>석탄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>갤럭시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가방매니아,김가방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>임기창</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>살까말까</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>개구리 뒷다리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>망치가방 70cm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -444,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
@@ -601,6 +673,164 @@
         <v>23</v>
       </c>
     </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>1012345644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>1027233444</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9">
+        <v>1022933444</v>
+      </c>
+      <c r="G9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10">
+        <v>1022233124</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11">
+        <v>1022233674</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12">
+        <v>1022673444</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13">
+        <v>1022933444</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
